--- a/PK/Exp2025-Cifar10-lr0.5-Dir0.5/resnet-dir0.5baseline_300.xlsx
+++ b/PK/Exp2025-Cifar10-lr0.5-Dir0.5/resnet-dir0.5baseline_300.xlsx
@@ -560,32 +560,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FedDocs</t>
+          <t>TiFL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>10.99</v>
+        <v>7.91</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>20.75</v>
+        <v>13.29</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
-        <v>46.32</v>
+        <v>29.26</v>
       </c>
       <c r="I4" t="n">
-        <v>111.45</v>
+        <v>87.02</v>
       </c>
       <c r="J4" t="n">
-        <v>72.73</v>
+        <v>74.45999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -596,68 +596,68 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>FedAvg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>16.33</v>
+        <v>15.5</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>25.68</v>
+        <v>21.33</v>
       </c>
       <c r="G5" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="H5" t="n">
-        <v>53.16</v>
+        <v>44.51</v>
       </c>
       <c r="I5" t="n">
-        <v>120.46</v>
+        <v>121.83</v>
       </c>
       <c r="J5" t="n">
-        <v>73.88</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nonIID(0.5)</t>
+          <t>nonIID(alpha0.66)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FedAvg</t>
+          <t>FedDocs</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>9.93</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>21.33</v>
+        <v>18.3</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H6" t="n">
-        <v>44.51</v>
+        <v>39.62</v>
       </c>
       <c r="I6" t="n">
-        <v>121.83</v>
+        <v>114.5</v>
       </c>
       <c r="J6" t="n">
-        <v>74.16</v>
+        <v>74.25</v>
       </c>
     </row>
   </sheetData>
